--- a/comp sci db project/paperwork/compsci db project schedule.xlsx
+++ b/comp sci db project/paperwork/compsci db project schedule.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aicperth-my.sharepoint.com/personal/22211_aic_wa_edu_au/Documents/Desktop/comp sci db project/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\comp sci db project\paperwork\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="14_{D048DD88-701B-405D-8BE0-6BC3A3401FEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{020AF929-44CF-421E-B225-2FD84B5879B2}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040"/>
   </bookViews>
   <sheets>
     <sheet name="Project schedule" sheetId="11" r:id="rId1"/>
@@ -26,7 +25,7 @@
     <definedName name="task_start" localSheetId="0">'Project schedule'!$D1</definedName>
     <definedName name="today" localSheetId="0">TODAY()</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -261,13 +260,13 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="5">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="m/d/yy;@"/>
-    <numFmt numFmtId="165" formatCode="ddd\,\ m/d/yyyy"/>
-    <numFmt numFmtId="166" formatCode="mmm\ d\,\ yyyy"/>
-    <numFmt numFmtId="167" formatCode="d"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="m/d/yy;@"/>
+    <numFmt numFmtId="166" formatCode="ddd\,\ m/d/yyyy"/>
+    <numFmt numFmtId="167" formatCode="mmm\ d\,\ yyyy"/>
+    <numFmt numFmtId="168" formatCode="d"/>
   </numFmts>
   <fonts count="29" x14ac:knownFonts="1">
     <font>
@@ -932,7 +931,7 @@
     </xf>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="2" applyFont="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" applyFont="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyProtection="0">
@@ -941,10 +940,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyProtection="0">
       <alignment horizontal="right" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="2">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="2">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyFill="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyFill="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyFill="0">
@@ -1019,13 +1018,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="167" fontId="18" fillId="12" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="12" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="18" fillId="12" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="12" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="18" fillId="12" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="12" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1047,10 +1046,10 @@
     <xf numFmtId="9" fontId="1" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="16" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1062,7 +1061,7 @@
     <xf numFmtId="9" fontId="1" fillId="3" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="6" xfId="10" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="165" fontId="16" fillId="3" borderId="6" xfId="10" applyFont="1" applyFill="1" applyBorder="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1071,7 +1070,7 @@
     <xf numFmtId="9" fontId="1" fillId="3" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="7" xfId="10" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="165" fontId="16" fillId="3" borderId="7" xfId="10" applyFont="1" applyFill="1" applyBorder="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1083,16 +1082,16 @@
     <xf numFmtId="9" fontId="1" fillId="7" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="16" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="4" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="4" borderId="5" xfId="10" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="165" fontId="16" fillId="4" borderId="5" xfId="10" applyFont="1" applyFill="1" applyBorder="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1101,10 +1100,10 @@
     <xf numFmtId="9" fontId="1" fillId="8" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="16" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1113,7 +1112,7 @@
     <xf numFmtId="9" fontId="1" fillId="5" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="5" borderId="8" xfId="10" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="165" fontId="16" fillId="5" borderId="8" xfId="10" applyFont="1" applyFill="1" applyBorder="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1122,10 +1121,10 @@
     <xf numFmtId="9" fontId="1" fillId="9" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="16" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1137,7 +1136,7 @@
     <xf numFmtId="9" fontId="1" fillId="10" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="10" borderId="9" xfId="10" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="165" fontId="16" fillId="10" borderId="9" xfId="10" applyFont="1" applyFill="1" applyBorder="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="12" applyFont="1" applyBorder="1">
@@ -1146,7 +1145,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="10" applyFont="1" applyBorder="1">
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="10" applyFont="1" applyBorder="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1155,10 +1154,10 @@
     <xf numFmtId="9" fontId="1" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1200,26 +1199,64 @@
     <xf numFmtId="0" fontId="16" fillId="5" borderId="8" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="12" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="24" fillId="0" borderId="0" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="167" fontId="16" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="16" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="16" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="24" fillId="0" borderId="0" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1227,72 +1264,34 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="16" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="16" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="16" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="18" fillId="12" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="13">
     <cellStyle name="Comma" xfId="4" builtinId="3" customBuiltin="1"/>
-    <cellStyle name="Date" xfId="10" xr:uid="{229918B6-DD13-4F5A-97B9-305F7E002AA3}"/>
+    <cellStyle name="Date" xfId="10"/>
     <cellStyle name="Heading 1" xfId="6" builtinId="16" customBuiltin="1"/>
     <cellStyle name="Heading 2" xfId="7" builtinId="17" customBuiltin="1"/>
     <cellStyle name="Heading 3" xfId="8" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8" customBuiltin="1"/>
-    <cellStyle name="Name" xfId="11" xr:uid="{B2D3C1EE-6B41-4801-AAFC-C2274E49E503}"/>
+    <cellStyle name="Name" xfId="11"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
-    <cellStyle name="Project Start" xfId="9" xr:uid="{8EB8A09A-C31C-40A3-B2C1-9449520178B8}"/>
-    <cellStyle name="Task" xfId="12" xr:uid="{6391D789-272B-4DD2-9BF3-2CDCF610FA41}"/>
+    <cellStyle name="Project Start" xfId="9"/>
+    <cellStyle name="Task" xfId="12"/>
     <cellStyle name="Title" xfId="5" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="zHiddenText" xfId="3" xr:uid="{26E66EE6-E33F-4D77-BAE4-0FB4F5BBF673}"/>
+    <cellStyle name="zHiddenText" xfId="3"/>
   </cellStyles>
   <dxfs count="18">
     <dxf>
@@ -1512,7 +1511,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="ToDoList" pivot="0" count="9" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+    <tableStyle name="ToDoList" pivot="0" count="9">
       <tableStyleElement type="wholeTable" dxfId="17"/>
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
@@ -1927,7 +1926,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1946,81 +1945,81 @@
   <sheetData>
     <row r="1" spans="1:63" ht="90" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A1" s="13"/>
-      <c r="B1" s="97" t="s">
+      <c r="B1" s="109" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
       <c r="E1" s="16"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="95" t="s">
+      <c r="H1" s="107" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="96"/>
-      <c r="J1" s="96"/>
-      <c r="K1" s="96"/>
-      <c r="L1" s="96"/>
-      <c r="M1" s="96"/>
-      <c r="N1" s="96"/>
+      <c r="I1" s="108"/>
+      <c r="J1" s="108"/>
+      <c r="K1" s="108"/>
+      <c r="L1" s="108"/>
+      <c r="M1" s="108"/>
+      <c r="N1" s="108"/>
       <c r="O1" s="19"/>
-      <c r="P1" s="94">
+      <c r="P1" s="101">
         <v>46218</v>
       </c>
-      <c r="Q1" s="93"/>
-      <c r="R1" s="93"/>
-      <c r="S1" s="93"/>
-      <c r="T1" s="93"/>
-      <c r="U1" s="93"/>
-      <c r="V1" s="93"/>
-      <c r="W1" s="93"/>
-      <c r="X1" s="93"/>
-      <c r="Y1" s="93"/>
-      <c r="Z1" s="113" t="s">
+      <c r="Q1" s="106"/>
+      <c r="R1" s="106"/>
+      <c r="S1" s="106"/>
+      <c r="T1" s="106"/>
+      <c r="U1" s="106"/>
+      <c r="V1" s="106"/>
+      <c r="W1" s="106"/>
+      <c r="X1" s="106"/>
+      <c r="Y1" s="106"/>
+      <c r="Z1" s="99" t="s">
         <v>66</v>
       </c>
-      <c r="AA1" s="114"/>
-      <c r="AB1" s="114"/>
-      <c r="AC1" s="114"/>
-      <c r="AD1" s="114"/>
-      <c r="AE1" s="114"/>
-      <c r="AG1" s="94" t="s">
+      <c r="AA1" s="100"/>
+      <c r="AB1" s="100"/>
+      <c r="AC1" s="100"/>
+      <c r="AD1" s="100"/>
+      <c r="AE1" s="100"/>
+      <c r="AG1" s="101" t="s">
         <v>67</v>
       </c>
-      <c r="AH1" s="94"/>
-      <c r="AI1" s="94"/>
-      <c r="AJ1" s="94"/>
-      <c r="AK1" s="94"/>
-      <c r="AL1" s="94"/>
-      <c r="AM1" s="94"/>
-      <c r="AN1" s="94"/>
+      <c r="AH1" s="101"/>
+      <c r="AI1" s="101"/>
+      <c r="AJ1" s="101"/>
+      <c r="AK1" s="101"/>
+      <c r="AL1" s="101"/>
+      <c r="AM1" s="101"/>
+      <c r="AN1" s="101"/>
     </row>
     <row r="2" spans="1:63" ht="30" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B2" s="75"/>
       <c r="C2" s="17"/>
       <c r="D2" s="18"/>
       <c r="E2" s="17"/>
-      <c r="H2" s="95" t="s">
+      <c r="H2" s="107" t="s">
         <v>21</v>
       </c>
-      <c r="I2" s="96"/>
-      <c r="J2" s="96"/>
-      <c r="K2" s="96"/>
-      <c r="L2" s="96"/>
-      <c r="M2" s="96"/>
-      <c r="N2" s="96"/>
+      <c r="I2" s="108"/>
+      <c r="J2" s="108"/>
+      <c r="K2" s="108"/>
+      <c r="L2" s="108"/>
+      <c r="M2" s="108"/>
+      <c r="N2" s="108"/>
       <c r="O2" s="19"/>
-      <c r="P2" s="92">
+      <c r="P2" s="105">
         <v>1</v>
       </c>
-      <c r="Q2" s="93"/>
-      <c r="R2" s="93"/>
-      <c r="S2" s="93"/>
-      <c r="T2" s="93"/>
-      <c r="U2" s="93"/>
-      <c r="V2" s="93"/>
-      <c r="W2" s="93"/>
-      <c r="X2" s="93"/>
-      <c r="Y2" s="93"/>
+      <c r="Q2" s="106"/>
+      <c r="R2" s="106"/>
+      <c r="S2" s="106"/>
+      <c r="T2" s="106"/>
+      <c r="U2" s="106"/>
+      <c r="V2" s="106"/>
+      <c r="W2" s="106"/>
+      <c r="X2" s="106"/>
+      <c r="Y2" s="106"/>
     </row>
     <row r="3" spans="1:63" s="21" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12"/>
@@ -2032,99 +2031,99 @@
       <c r="A4" s="13"/>
       <c r="B4" s="24"/>
       <c r="D4" s="25"/>
-      <c r="H4" s="100">
+      <c r="H4" s="104">
         <f>H5</f>
         <v>46216</v>
       </c>
-      <c r="I4" s="98"/>
-      <c r="J4" s="98"/>
-      <c r="K4" s="98"/>
-      <c r="L4" s="98"/>
-      <c r="M4" s="98"/>
-      <c r="N4" s="98"/>
-      <c r="O4" s="98">
+      <c r="I4" s="102"/>
+      <c r="J4" s="102"/>
+      <c r="K4" s="102"/>
+      <c r="L4" s="102"/>
+      <c r="M4" s="102"/>
+      <c r="N4" s="102"/>
+      <c r="O4" s="102">
         <f>O5</f>
         <v>46223</v>
       </c>
-      <c r="P4" s="98"/>
-      <c r="Q4" s="98"/>
-      <c r="R4" s="98"/>
-      <c r="S4" s="98"/>
-      <c r="T4" s="98"/>
-      <c r="U4" s="98"/>
-      <c r="V4" s="98">
+      <c r="P4" s="102"/>
+      <c r="Q4" s="102"/>
+      <c r="R4" s="102"/>
+      <c r="S4" s="102"/>
+      <c r="T4" s="102"/>
+      <c r="U4" s="102"/>
+      <c r="V4" s="102">
         <f>V5</f>
         <v>46230</v>
       </c>
-      <c r="W4" s="98"/>
-      <c r="X4" s="98"/>
-      <c r="Y4" s="98"/>
-      <c r="Z4" s="98"/>
-      <c r="AA4" s="98"/>
-      <c r="AB4" s="98"/>
-      <c r="AC4" s="98">
+      <c r="W4" s="102"/>
+      <c r="X4" s="102"/>
+      <c r="Y4" s="102"/>
+      <c r="Z4" s="102"/>
+      <c r="AA4" s="102"/>
+      <c r="AB4" s="102"/>
+      <c r="AC4" s="102">
         <f>AC5</f>
         <v>46237</v>
       </c>
-      <c r="AD4" s="98"/>
-      <c r="AE4" s="98"/>
-      <c r="AF4" s="98"/>
-      <c r="AG4" s="98"/>
-      <c r="AH4" s="98"/>
-      <c r="AI4" s="98"/>
-      <c r="AJ4" s="98">
+      <c r="AD4" s="102"/>
+      <c r="AE4" s="102"/>
+      <c r="AF4" s="102"/>
+      <c r="AG4" s="102"/>
+      <c r="AH4" s="102"/>
+      <c r="AI4" s="102"/>
+      <c r="AJ4" s="102">
         <f>AJ5</f>
         <v>46244</v>
       </c>
-      <c r="AK4" s="98"/>
-      <c r="AL4" s="98"/>
-      <c r="AM4" s="98"/>
-      <c r="AN4" s="98"/>
-      <c r="AO4" s="98"/>
-      <c r="AP4" s="98"/>
-      <c r="AQ4" s="98">
+      <c r="AK4" s="102"/>
+      <c r="AL4" s="102"/>
+      <c r="AM4" s="102"/>
+      <c r="AN4" s="102"/>
+      <c r="AO4" s="102"/>
+      <c r="AP4" s="102"/>
+      <c r="AQ4" s="102">
         <f>AQ5</f>
         <v>46251</v>
       </c>
-      <c r="AR4" s="98"/>
-      <c r="AS4" s="98"/>
-      <c r="AT4" s="98"/>
-      <c r="AU4" s="98"/>
-      <c r="AV4" s="98"/>
-      <c r="AW4" s="98"/>
-      <c r="AX4" s="98">
+      <c r="AR4" s="102"/>
+      <c r="AS4" s="102"/>
+      <c r="AT4" s="102"/>
+      <c r="AU4" s="102"/>
+      <c r="AV4" s="102"/>
+      <c r="AW4" s="102"/>
+      <c r="AX4" s="102">
         <f>AX5</f>
         <v>46258</v>
       </c>
-      <c r="AY4" s="98"/>
-      <c r="AZ4" s="98"/>
-      <c r="BA4" s="98"/>
-      <c r="BB4" s="98"/>
-      <c r="BC4" s="98"/>
-      <c r="BD4" s="98"/>
-      <c r="BE4" s="98">
+      <c r="AY4" s="102"/>
+      <c r="AZ4" s="102"/>
+      <c r="BA4" s="102"/>
+      <c r="BB4" s="102"/>
+      <c r="BC4" s="102"/>
+      <c r="BD4" s="102"/>
+      <c r="BE4" s="102">
         <f>BE5</f>
         <v>46265</v>
       </c>
-      <c r="BF4" s="98"/>
-      <c r="BG4" s="98"/>
-      <c r="BH4" s="98"/>
-      <c r="BI4" s="98"/>
-      <c r="BJ4" s="98"/>
-      <c r="BK4" s="99"/>
+      <c r="BF4" s="102"/>
+      <c r="BG4" s="102"/>
+      <c r="BH4" s="102"/>
+      <c r="BI4" s="102"/>
+      <c r="BJ4" s="102"/>
+      <c r="BK4" s="103"/>
     </row>
     <row r="5" spans="1:63" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="87"/>
-      <c r="B5" s="88" t="s">
+      <c r="A5" s="110"/>
+      <c r="B5" s="111" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="90" t="s">
+      <c r="C5" s="113" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="90" t="s">
+      <c r="D5" s="113" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="90" t="s">
+      <c r="E5" s="113" t="s">
         <v>4</v>
       </c>
       <c r="H5" s="26">
@@ -2255,7 +2254,7 @@
         <f t="shared" si="0"/>
         <v>46247</v>
       </c>
-      <c r="AN5" s="105">
+      <c r="AN5" s="91">
         <f t="shared" si="0"/>
         <v>46248</v>
       </c>
@@ -2353,11 +2352,11 @@
       </c>
     </row>
     <row r="6" spans="1:63" s="21" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="87"/>
-      <c r="B6" s="89"/>
-      <c r="C6" s="91"/>
-      <c r="D6" s="91"/>
-      <c r="E6" s="91"/>
+      <c r="A6" s="110"/>
+      <c r="B6" s="112"/>
+      <c r="C6" s="114"/>
+      <c r="D6" s="114"/>
+      <c r="E6" s="114"/>
       <c r="H6" s="29" t="str">
         <f t="shared" ref="H6:AM6" si="3">LEFT(TEXT(H5,"ddd"),1)</f>
         <v>M</v>
@@ -2486,7 +2485,7 @@
         <f t="shared" si="3"/>
         <v>T</v>
       </c>
-      <c r="AN6" s="107" t="str">
+      <c r="AN6" s="93" t="str">
         <f t="shared" ref="AN6:BK6" si="4">LEFT(TEXT(AN5,"ddd"),1)</f>
         <v>F</v>
       </c>
@@ -2626,9 +2625,9 @@
       <c r="AJ7" s="33"/>
       <c r="AK7" s="33"/>
       <c r="AL7" s="33"/>
-      <c r="AM7" s="101"/>
-      <c r="AN7" s="108"/>
-      <c r="AO7" s="103"/>
+      <c r="AM7" s="87"/>
+      <c r="AN7" s="94"/>
+      <c r="AO7" s="89"/>
       <c r="AP7" s="33"/>
       <c r="AQ7" s="33"/>
       <c r="AR7" s="33"/>
@@ -2697,7 +2696,7 @@
       <c r="AK8" s="38"/>
       <c r="AL8" s="38"/>
       <c r="AM8" s="38"/>
-      <c r="AN8" s="109"/>
+      <c r="AN8" s="95"/>
       <c r="AO8" s="38"/>
       <c r="AP8" s="38"/>
       <c r="AQ8" s="38"/>
@@ -2774,9 +2773,9 @@
       <c r="AJ9" s="42"/>
       <c r="AK9" s="42"/>
       <c r="AL9" s="42"/>
-      <c r="AM9" s="102"/>
-      <c r="AN9" s="110"/>
-      <c r="AO9" s="104"/>
+      <c r="AM9" s="88"/>
+      <c r="AN9" s="96"/>
+      <c r="AO9" s="90"/>
       <c r="AP9" s="42"/>
       <c r="AQ9" s="42"/>
       <c r="AR9" s="42"/>
@@ -2852,9 +2851,9 @@
       <c r="AJ10" s="42"/>
       <c r="AK10" s="42"/>
       <c r="AL10" s="42"/>
-      <c r="AM10" s="102"/>
-      <c r="AN10" s="110"/>
-      <c r="AO10" s="104"/>
+      <c r="AM10" s="88"/>
+      <c r="AN10" s="96"/>
+      <c r="AO10" s="90"/>
       <c r="AP10" s="42"/>
       <c r="AQ10" s="42"/>
       <c r="AR10" s="42"/>
@@ -2930,9 +2929,9 @@
       <c r="AJ11" s="42"/>
       <c r="AK11" s="42"/>
       <c r="AL11" s="42"/>
-      <c r="AM11" s="102"/>
-      <c r="AN11" s="110"/>
-      <c r="AO11" s="104"/>
+      <c r="AM11" s="88"/>
+      <c r="AN11" s="96"/>
+      <c r="AO11" s="90"/>
       <c r="AP11" s="42"/>
       <c r="AQ11" s="42"/>
       <c r="AR11" s="42"/>
@@ -3008,9 +3007,9 @@
       <c r="AJ12" s="42"/>
       <c r="AK12" s="42"/>
       <c r="AL12" s="42"/>
-      <c r="AM12" s="102"/>
-      <c r="AN12" s="110"/>
-      <c r="AO12" s="104"/>
+      <c r="AM12" s="88"/>
+      <c r="AN12" s="96"/>
+      <c r="AO12" s="90"/>
       <c r="AP12" s="42"/>
       <c r="AQ12" s="42"/>
       <c r="AR12" s="42"/>
@@ -3086,9 +3085,9 @@
       <c r="AJ13" s="42"/>
       <c r="AK13" s="42"/>
       <c r="AL13" s="42"/>
-      <c r="AM13" s="102"/>
-      <c r="AN13" s="110"/>
-      <c r="AO13" s="104"/>
+      <c r="AM13" s="88"/>
+      <c r="AN13" s="96"/>
+      <c r="AO13" s="90"/>
       <c r="AP13" s="42"/>
       <c r="AQ13" s="42"/>
       <c r="AR13" s="42"/>
@@ -3118,7 +3117,7 @@
         <v>55</v>
       </c>
       <c r="C14" s="43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" s="44">
         <f>E13</f>
@@ -3164,9 +3163,9 @@
       <c r="AJ14" s="42"/>
       <c r="AK14" s="42"/>
       <c r="AL14" s="42"/>
-      <c r="AM14" s="102"/>
-      <c r="AN14" s="110"/>
-      <c r="AO14" s="104"/>
+      <c r="AM14" s="88"/>
+      <c r="AN14" s="96"/>
+      <c r="AO14" s="90"/>
       <c r="AP14" s="42"/>
       <c r="AQ14" s="42"/>
       <c r="AR14" s="42"/>
@@ -3203,7 +3202,7 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AN15" s="108"/>
+      <c r="AN15" s="94"/>
     </row>
     <row r="16" spans="1:63" s="39" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="13"/>
@@ -3257,9 +3256,9 @@
       <c r="AJ16" s="42"/>
       <c r="AK16" s="42"/>
       <c r="AL16" s="42"/>
-      <c r="AM16" s="102"/>
-      <c r="AN16" s="110"/>
-      <c r="AO16" s="104"/>
+      <c r="AM16" s="88"/>
+      <c r="AN16" s="96"/>
+      <c r="AO16" s="90"/>
       <c r="AP16" s="42"/>
       <c r="AQ16" s="42"/>
       <c r="AR16" s="42"/>
@@ -3335,9 +3334,9 @@
       <c r="AJ17" s="42"/>
       <c r="AK17" s="42"/>
       <c r="AL17" s="42"/>
-      <c r="AM17" s="102"/>
-      <c r="AN17" s="110"/>
-      <c r="AO17" s="104"/>
+      <c r="AM17" s="88"/>
+      <c r="AN17" s="96"/>
+      <c r="AO17" s="90"/>
       <c r="AP17" s="42"/>
       <c r="AQ17" s="42"/>
       <c r="AR17" s="42"/>
@@ -3413,9 +3412,9 @@
       <c r="AJ18" s="42"/>
       <c r="AK18" s="42"/>
       <c r="AL18" s="42"/>
-      <c r="AM18" s="102"/>
-      <c r="AN18" s="110"/>
-      <c r="AO18" s="104"/>
+      <c r="AM18" s="88"/>
+      <c r="AN18" s="96"/>
+      <c r="AO18" s="90"/>
       <c r="AP18" s="42"/>
       <c r="AQ18" s="42"/>
       <c r="AR18" s="42"/>
@@ -3491,9 +3490,9 @@
       <c r="AJ19" s="42"/>
       <c r="AK19" s="42"/>
       <c r="AL19" s="42"/>
-      <c r="AM19" s="102"/>
-      <c r="AN19" s="110"/>
-      <c r="AO19" s="104"/>
+      <c r="AM19" s="88"/>
+      <c r="AN19" s="96"/>
+      <c r="AO19" s="90"/>
       <c r="AP19" s="42"/>
       <c r="AQ19" s="42"/>
       <c r="AR19" s="42"/>
@@ -3569,9 +3568,9 @@
       <c r="AJ20" s="42"/>
       <c r="AK20" s="42"/>
       <c r="AL20" s="42"/>
-      <c r="AM20" s="102"/>
-      <c r="AN20" s="110"/>
-      <c r="AO20" s="104"/>
+      <c r="AM20" s="88"/>
+      <c r="AN20" s="96"/>
+      <c r="AO20" s="90"/>
       <c r="AP20" s="42"/>
       <c r="AQ20" s="42"/>
       <c r="AR20" s="42"/>
@@ -3640,7 +3639,7 @@
       <c r="AK21" s="56"/>
       <c r="AL21" s="56"/>
       <c r="AM21" s="56"/>
-      <c r="AN21" s="111"/>
+      <c r="AN21" s="97"/>
       <c r="AO21" s="56"/>
       <c r="AP21" s="56"/>
       <c r="AQ21" s="56"/>
@@ -3671,7 +3670,7 @@
         <v>58</v>
       </c>
       <c r="C22" s="57">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="D22" s="58">
         <v>46226</v>
@@ -3716,9 +3715,9 @@
       <c r="AJ22" s="42"/>
       <c r="AK22" s="42"/>
       <c r="AL22" s="42"/>
-      <c r="AM22" s="102"/>
-      <c r="AN22" s="110"/>
-      <c r="AO22" s="104"/>
+      <c r="AM22" s="88"/>
+      <c r="AN22" s="96"/>
+      <c r="AO22" s="90"/>
       <c r="AP22" s="42"/>
       <c r="AQ22" s="42"/>
       <c r="AR22" s="42"/>
@@ -3794,9 +3793,9 @@
       <c r="AJ23" s="42"/>
       <c r="AK23" s="42"/>
       <c r="AL23" s="42"/>
-      <c r="AM23" s="102"/>
-      <c r="AN23" s="110"/>
-      <c r="AO23" s="104"/>
+      <c r="AM23" s="88"/>
+      <c r="AN23" s="96"/>
+      <c r="AO23" s="90"/>
       <c r="AP23" s="42"/>
       <c r="AQ23" s="42"/>
       <c r="AR23" s="42"/>
@@ -3872,9 +3871,9 @@
       <c r="AJ24" s="42"/>
       <c r="AK24" s="42"/>
       <c r="AL24" s="42"/>
-      <c r="AM24" s="102"/>
-      <c r="AN24" s="110"/>
-      <c r="AO24" s="104"/>
+      <c r="AM24" s="88"/>
+      <c r="AN24" s="96"/>
+      <c r="AO24" s="90"/>
       <c r="AP24" s="42"/>
       <c r="AQ24" s="42"/>
       <c r="AR24" s="42"/>
@@ -3943,7 +3942,7 @@
       <c r="AK25" s="63"/>
       <c r="AL25" s="63"/>
       <c r="AM25" s="63"/>
-      <c r="AN25" s="110"/>
+      <c r="AN25" s="96"/>
       <c r="AO25" s="63"/>
       <c r="AP25" s="63"/>
       <c r="AQ25" s="63"/>
@@ -4020,9 +4019,9 @@
       <c r="AJ26" s="42"/>
       <c r="AK26" s="42"/>
       <c r="AL26" s="42"/>
-      <c r="AM26" s="102"/>
-      <c r="AN26" s="110"/>
-      <c r="AO26" s="104"/>
+      <c r="AM26" s="88"/>
+      <c r="AN26" s="96"/>
+      <c r="AO26" s="90"/>
       <c r="AP26" s="42"/>
       <c r="AQ26" s="42"/>
       <c r="AR26" s="42"/>
@@ -4098,9 +4097,9 @@
       <c r="AJ27" s="42"/>
       <c r="AK27" s="42"/>
       <c r="AL27" s="42"/>
-      <c r="AM27" s="102"/>
-      <c r="AN27" s="110"/>
-      <c r="AO27" s="104"/>
+      <c r="AM27" s="88"/>
+      <c r="AN27" s="96"/>
+      <c r="AO27" s="90"/>
       <c r="AP27" s="42"/>
       <c r="AQ27" s="42"/>
       <c r="AR27" s="42"/>
@@ -4176,9 +4175,9 @@
       <c r="AJ28" s="42"/>
       <c r="AK28" s="42"/>
       <c r="AL28" s="42"/>
-      <c r="AM28" s="102"/>
-      <c r="AN28" s="110"/>
-      <c r="AO28" s="104"/>
+      <c r="AM28" s="88"/>
+      <c r="AN28" s="96"/>
+      <c r="AO28" s="90"/>
       <c r="AP28" s="42"/>
       <c r="AQ28" s="42"/>
       <c r="AR28" s="42"/>
@@ -4254,9 +4253,9 @@
       <c r="AJ29" s="42"/>
       <c r="AK29" s="42"/>
       <c r="AL29" s="42"/>
-      <c r="AM29" s="102"/>
-      <c r="AN29" s="110"/>
-      <c r="AO29" s="104"/>
+      <c r="AM29" s="88"/>
+      <c r="AN29" s="96"/>
+      <c r="AO29" s="90"/>
       <c r="AP29" s="42"/>
       <c r="AQ29" s="42"/>
       <c r="AR29" s="42"/>
@@ -4332,9 +4331,9 @@
       <c r="AJ30" s="42"/>
       <c r="AK30" s="42"/>
       <c r="AL30" s="42"/>
-      <c r="AM30" s="102"/>
-      <c r="AN30" s="112"/>
-      <c r="AO30" s="104"/>
+      <c r="AM30" s="88"/>
+      <c r="AN30" s="98"/>
+      <c r="AO30" s="90"/>
       <c r="AP30" s="42"/>
       <c r="AQ30" s="42"/>
       <c r="AR30" s="42"/>
@@ -4401,7 +4400,7 @@
       <c r="AK31" s="38"/>
       <c r="AL31" s="38"/>
       <c r="AM31" s="38"/>
-      <c r="AN31" s="106"/>
+      <c r="AN31" s="92"/>
       <c r="AO31" s="38"/>
       <c r="AP31" s="38"/>
       <c r="AQ31" s="38"/>
@@ -4504,6 +4503,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
     <mergeCell ref="Z1:AE1"/>
     <mergeCell ref="AG1:AN1"/>
     <mergeCell ref="BE4:BK4"/>
@@ -4518,12 +4523,6 @@
     <mergeCell ref="P1:Y1"/>
     <mergeCell ref="H1:N1"/>
     <mergeCell ref="H2:N2"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C32">
     <cfRule type="dataBar" priority="23">
@@ -4577,21 +4576,21 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="13">
-    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" promptTitle="Display Week" prompt="Changing this number will scroll the Gantt Chart view." sqref="P2" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" promptTitle="Display Week" prompt="Changing this number will scroll the Gantt Chart view." sqref="P2">
       <formula1>1</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Create a Project Schedule in this worksheet._x000a_Enter title of this project in cell B1. _x000a_Information on how to use this worksheet, including instructions for screen readers and the author of this workbook, is in the About worksheet._x000a_" sqref="A1" xr:uid="{D005F8F4-EA16-4627-8A05-1997BE425B88}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter Company name in cel B2." sqref="A2" xr:uid="{75F274B0-5B30-4CC0-A53C-C012C0845179}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter the name of the Project Lead in cell C3. Enter the Project Start date in cell Q1. Project Start: label is in cell I1." sqref="A3" xr:uid="{EEA7C783-457F-401F-98B9-9035587B9210}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="The Display week in cell Q2 is the starting week to display in the project schedule in cell I4. The project start date is Week 1. To change the display week, enter a new week number in cell Q2._x000a__x000a_Start date for each week is auto calculated starting in I4." sqref="A4" xr:uid="{43382715-6BC7-4B19-A31B-4B13A11ED166}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Cells I5 through BL5 contain the day number for the week represented in the cell block above each date and are auto calculated._x000a__x000a_Today's date is outlined from today's date in row 5 through the entire date column to the end of the project schedule." sqref="A5:A6" xr:uid="{7A3789A6-A3FB-43B6-A4F7-8C0AC564F67E}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Cell B8 contains the Phase 1 sample title. Enter a new title in cell B8._x000a_To delete the phase and work only from tasks, simply delete this row." sqref="A8" xr:uid="{CEC78982-AFA8-419E-B0A2-676B709E5100}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="B9 contains the task name.  C9 is the assignee.  D9 is a progress bar that shades based on the number entered into the cell.  _x000a__x000a_E9 contains the start date and F9 contains the end date._x000a__x000a_The Gantt chart will fill in starting in cell I9 based on task dates." sqref="A9" xr:uid="{D870A2F6-6B07-4F5A-A81D-4BCCFADF8796}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Rows 10 through 13 repeat the pattern from row 9. _x000a__x000a_Repeat the instructions from cell A9 for all task rows in this worksheet. _x000a__x000a_Continue entering tasks in cells A10 through A13 or go to cell A14 to learn more." sqref="A10" xr:uid="{872449A7-C3CC-45B6-BA90-B1AAD66BA0E5}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Cell B14 contains the Phase 2 sample title. Enter a new title in cell B14._x000a_To delete the phase and work only from tasks, simply delete this row. To remove the phase, simply delete the row. Add tasks to previous phase by entering a new row above this one._x000a_" sqref="A15" xr:uid="{4F48FC41-E335-47F1-87AA-3333A52AD81C}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Phase 3's sample block starts in cell B20." sqref="A21" xr:uid="{956902D1-D3B5-416D-BB69-9362D193BC0A}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Phase 4's sample block starts in cell B26." sqref="A25" xr:uid="{DE54E5DE-526D-4D71-8D03-E99B4AB2FEE5}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="This row marks the end of the Project Schedule. DO NOT enter anything in this row. _x000a_Insert new rows ABOVE this one to continue building out your Project Schedule." sqref="A32" xr:uid="{79B9237E-4DD3-4E0F-8ED6-E0B695A99D96}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Create a Project Schedule in this worksheet._x000a_Enter title of this project in cell B1. _x000a_Information on how to use this worksheet, including instructions for screen readers and the author of this workbook, is in the About worksheet._x000a_" sqref="A1"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter Company name in cel B2." sqref="A2"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter the name of the Project Lead in cell C3. Enter the Project Start date in cell Q1. Project Start: label is in cell I1." sqref="A3"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="The Display week in cell Q2 is the starting week to display in the project schedule in cell I4. The project start date is Week 1. To change the display week, enter a new week number in cell Q2._x000a__x000a_Start date for each week is auto calculated starting in I4." sqref="A4"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Cells I5 through BL5 contain the day number for the week represented in the cell block above each date and are auto calculated._x000a__x000a_Today's date is outlined from today's date in row 5 through the entire date column to the end of the project schedule." sqref="A5:A6"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Cell B8 contains the Phase 1 sample title. Enter a new title in cell B8._x000a_To delete the phase and work only from tasks, simply delete this row." sqref="A8"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="B9 contains the task name.  C9 is the assignee.  D9 is a progress bar that shades based on the number entered into the cell.  _x000a__x000a_E9 contains the start date and F9 contains the end date._x000a__x000a_The Gantt chart will fill in starting in cell I9 based on task dates." sqref="A9"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Rows 10 through 13 repeat the pattern from row 9. _x000a__x000a_Repeat the instructions from cell A9 for all task rows in this worksheet. _x000a__x000a_Continue entering tasks in cells A10 through A13 or go to cell A14 to learn more." sqref="A10"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Cell B14 contains the Phase 2 sample title. Enter a new title in cell B14._x000a_To delete the phase and work only from tasks, simply delete this row. To remove the phase, simply delete the row. Add tasks to previous phase by entering a new row above this one._x000a_" sqref="A15"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Phase 3's sample block starts in cell B20." sqref="A21"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Phase 4's sample block starts in cell B26." sqref="A25"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="This row marks the end of the Project Schedule. DO NOT enter anything in this row. _x000a_Insert new rows ABOVE this one to continue building out your Project Schedule." sqref="A32"/>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.35" right="0.35" top="0.35" bottom="0.5" header="0.3" footer="0.3"/>
@@ -4624,7 +4623,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{106ECBF7-9B5B-493D-BC97-7D471FEF0A34}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
@@ -4735,7 +4734,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
@@ -4845,9 +4844,9 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A13" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
-    <hyperlink ref="A10" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
-    <hyperlink ref="A2" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
+    <hyperlink ref="A13" r:id="rId1"/>
+    <hyperlink ref="A10" r:id="rId2"/>
+    <hyperlink ref="A2" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId4"/>
@@ -4856,18 +4855,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5015,14 +5014,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97245281-08F3-4104-84BD-39F3D8CFB195}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A82239A0-E68C-493F-BEE6-C77FEA397FD6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
@@ -5034,6 +5025,14 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97245281-08F3-4104-84BD-39F3D8CFB195}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
